--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>99769</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453463.1360002308</v>
+        <v>453463</v>
       </c>
       <c r="R2" t="n">
-        <v>6396682.429467101</v>
+        <v>6396682</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102066</v>
+        <v>102072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102072</v>
+        <v>102073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102073</v>
+        <v>102100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102100</v>
+        <v>102106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102106</v>
+        <v>102113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102113</v>
+        <v>102117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102117</v>
+        <v>102124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102127</v>
+        <v>102132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102132</v>
+        <v>102140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28604-2025 artfynd.xlsx
+++ b/artfynd/A 28604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74000890</v>
       </c>
       <c r="B2" t="n">
-        <v>102140</v>
+        <v>102150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
